--- a/docs/releases/v1.1.0-phase1-full-info.xlsx
+++ b/docs/releases/v1.1.0-phase1-full-info.xlsx
@@ -17,13 +17,14 @@
     <sheet sheetId="11" name="10-质量指标" state="visible" r:id="rId14"/>
     <sheet sheetId="12" name="11-关键里程碑" state="visible" r:id="rId15"/>
     <sheet sheetId="13" name="12-下一阶段规划" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="13-版本状态总览" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="451">
   <si>
     <t>项目</t>
   </si>
@@ -1154,6 +1155,228 @@
   </si>
   <si>
     <t>本地缓存策略</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>✅ 可用</t>
+  </si>
+  <si>
+    <t>iOS</t>
+  </si>
+  <si>
+    <t>🚧 未完整测试</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>❌ 非目标平台</t>
+  </si>
+  <si>
+    <t>fc437bd</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>【已完成功能 - 基础功能】</t>
+  </si>
+  <si>
+    <t>【描述】</t>
+  </si>
+  <si>
+    <t>文本对话</t>
+  </si>
+  <si>
+    <t>完整聊天界面，实时消息收发，消息历史显示</t>
+  </si>
+  <si>
+    <t>语音对话 · 录音</t>
+  </si>
+  <si>
+    <t>Android 原生 AudioRecord，48kHz 采集，VAD 检测</t>
+  </si>
+  <si>
+    <t>语音对话 · 播放</t>
+  </si>
+  <si>
+    <t>PCM 音频流实时播放，48kHz AudioTrack</t>
+  </si>
+  <si>
+    <t>实时重采样</t>
+  </si>
+  <si>
+    <t>48kHz → 16kHz 自动重采样后上传</t>
+  </si>
+  <si>
+    <t>WebSocket 通信</t>
+  </si>
+  <si>
+    <t>与后端双向实时通信，断线重连，JSON/Binary 混合帧</t>
+  </si>
+  <si>
+    <t>Live2D 角色渲染</t>
+  </si>
+  <si>
+    <t>Cubism SDK 集成，角色模型显示与动画</t>
+  </si>
+  <si>
+    <t>唇同步（LipSync）</t>
+  </si>
+  <si>
+    <t>音频振幅实时驱动角色口型，低延迟</t>
+  </si>
+  <si>
+    <t>QR 扫码连接</t>
+  </si>
+  <si>
+    <t>扫 nekorn:// deep link，自动写入后端配置并跳主界面</t>
+  </si>
+  <si>
+    <t>麦克风权限管理</t>
+  </si>
+  <si>
+    <t>友好弹窗、拒绝后引导跳设置、延迟请求避免冲突</t>
+  </si>
+  <si>
+    <t>音频诊断工具</t>
+  </si>
+  <si>
+    <t>/audio-debug 页面：采样率检测、错误报告</t>
+  </si>
+  <si>
+    <t>跨平台音频架构</t>
+  </si>
+  <si>
+    <t>@project_neko/audio-service，Native/Web 双实现</t>
+  </si>
+  <si>
+    <t>原生 PCM 模块</t>
+  </si>
+  <si>
+    <t>react-native-pcm-stream，Kotlin 实现</t>
+  </si>
+  <si>
+    <t>【阶段一新增功能】</t>
+  </si>
+  <si>
+    <t>Live2D 双指手势</t>
+  </si>
+  <si>
+    <t>支持双指拖动、缩放 Live2D 模型，GestureHandler 集成</t>
+  </si>
+  <si>
+    <t>用户说话打断 AI 回复，实时停止音频播放，完整打断链路</t>
+  </si>
+  <si>
+    <t>动态切换 Live2D 模型，自动清空音频队列，事件驱动架构</t>
+  </si>
+  <si>
+    <t>语音模式就绪提示，脉冲动画视觉反馈</t>
+  </si>
+  <si>
+    <t>RN 端支持自定义音频格式，灵活的编解码配置</t>
+  </si>
+  <si>
+    <t>文本 TTS 修复</t>
+  </si>
+  <si>
+    <t>修复文本模式下 TTS 音频丢失问题，绕过服务端 speech_id bug</t>
+  </si>
+  <si>
+    <t>WebSocket 二进制</t>
+  </si>
+  <si>
+    <t>修复 RN 端 WebSocket 接收二进制数据问题</t>
+  </si>
+  <si>
+    <t>Session 生命周期</t>
+  </si>
+  <si>
+    <t>完善会话管理，角色切换清空音频，防竞态保护</t>
+  </si>
+  <si>
+    <t>FRP 反向代理</t>
+  </si>
+  <si>
+    <t>支持 FRP 内网穿透，方便真机调试和开发</t>
+  </si>
+  <si>
+    <t>.env 文件支持，灵活的开发连接参数配置</t>
+  </si>
+  <si>
+    <t>本地连接存储</t>
+  </si>
+  <si>
+    <t>DevConnectionStorage 本地持久化开发配置</t>
+  </si>
+  <si>
+    <t>统一 API 地址</t>
+  </si>
+  <si>
+    <t>buildHttpBaseURL 统一管理 API 地址构建</t>
+  </si>
+  <si>
+    <t>【总体状态评估】</t>
+  </si>
+  <si>
+    <t>【说明】</t>
+  </si>
+  <si>
+    <t>核心对话体验</t>
+  </si>
+  <si>
+    <t>✅ 完整 | 文字 + 语音双模式，WebSocket 稳定，Live2D 渲染正常</t>
+  </si>
+  <si>
+    <t>✅ 增强 | Live2D 手势操作流畅，角色切换联动完整</t>
+  </si>
+  <si>
+    <t>对话流畅性</t>
+  </si>
+  <si>
+    <t>✅ 改进 | 语音打断功能上线，用户可随时打断 AI</t>
+  </si>
+  <si>
+    <t>✅ 提升 | TTS 音频丢失已修复，WebSocket 二进制接收正常，稳定性 95%</t>
+  </si>
+  <si>
+    <t>角色系统</t>
+  </si>
+  <si>
+    <t>✅ 完整 | 角色切换 + Live2D 模型联动 + 音频清空完整实现</t>
+  </si>
+  <si>
+    <t>Android 可用性</t>
+  </si>
+  <si>
+    <t>✅ 可用 | 核心功能验证通过，多机型测试待做</t>
+  </si>
+  <si>
+    <t>iOS 可用性</t>
+  </si>
+  <si>
+    <t>🚧 未测 | 未在真机完整验证，需 Xcode + 证书配置</t>
+  </si>
+  <si>
+    <t>✅ 优化 | 完整文档体系，FRP 支持，环境变量配置</t>
+  </si>
+  <si>
+    <t>✅ 完整 | 新手指南 + 技术文档 + 链路分析，覆盖率 95%</t>
+  </si>
+  <si>
+    <t>发布就绪度</t>
+  </si>
+  <si>
+    <t>⏳ 阶段一 | 阶段一功能完整，可发布内测版本</t>
+  </si>
+  <si>
+    <t>功能完整度</t>
+  </si>
+  <si>
+    <t>MVP+ 级 | 扫码连接/对话/Live2D/手势/打断/角色切换已齐，图片/后台音频等待阶段二</t>
   </si>
 </sst>
 </file>
@@ -2203,6 +2426,413 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B49"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D15"/>
